--- a/branches/updated-examples/ValueSet-MycoplasmaCodes.xlsx
+++ b/branches/updated-examples/ValueSet-MycoplasmaCodes.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-24T11:01:18+00:00</t>
+    <t>2025-04-06T05:59:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/updated-examples/ValueSet-MycoplasmaCodes.xlsx
+++ b/branches/updated-examples/ValueSet-MycoplasmaCodes.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-06T05:59:28+00:00</t>
+    <t>2025-04-06T06:02:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
